--- a/healthcare_surveys/030_pediatric_eye_care_feedback_form--healthcare_surveys.xlsx
+++ b/healthcare_surveys/030_pediatric_eye_care_feedback_form--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'parent',_'label':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'parent', 'label': 'Parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'guardian',_'label':_'guardian'}</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'guardian', 'label': 'Guardian'}</t>
+          <t>Guardian</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'0-1',_'label':_'0-1'}</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': '0-1', 'label': '0-1'}</t>
+          <t>0-1</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'2-4',_'label':_'2-4'}</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': '2-4', 'label': '2-4'}</t>
+          <t>2-4</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'5-10',_'label':_'5-10'}</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': '5-10', 'label': '5-10'}</t>
+          <t>5-10</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'11-16',_'label':_'11-16'}</t>
+          <t>11-16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': '11-16', 'label': '11-16'}</t>
+          <t>11-16</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'17-24',_'label':_'17-24'}</t>
+          <t>17-24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': '17-24', 'label': '17-24'}</t>
+          <t>17-24</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'25+',_'label':_'25+'}</t>
+          <t>25+</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': '25+', 'label': '25+'}</t>
+          <t>25+</t>
         </is>
       </c>
     </row>
